--- a/DC30.xlsx
+++ b/DC30.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://santos.sharepoint.com/sites/Dev-CoopOil/Shared Documents/Limestone Creek (Area)/McKinlay/Horizontal Well Sample Description Spreadsheets/Well Tops/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_54FD8076D0100871E25E9059C5D8B2B3BC81284F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC134588-D971-4FD0-96B6-B9E2BADAB8CB}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_54FD8076D0100871E25E9059C5D8B2B3BC81284F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAA3F9BA-8BC0-4F00-9E3A-C23150C18773}"/>
   <bookViews>
-    <workbookView xWindow="19530" yWindow="4305" windowWidth="26850" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8130" yWindow="2865" windowWidth="21405" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="67">
   <si>
     <t>Well identifier (Well name)</t>
   </si>
@@ -201,6 +201,42 @@
   </si>
   <si>
     <t>TERINGIE 6</t>
+  </si>
+  <si>
+    <t>MCKINLAY 10</t>
+  </si>
+  <si>
+    <t>GRACA</t>
+  </si>
+  <si>
+    <t>Matches McKinlay pick. Corresponds to a Gr/Resistivity and sonic shift to the right. First penetration of marker entered.</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>MCKINLAY 11</t>
+  </si>
+  <si>
+    <t>Santos</t>
+  </si>
+  <si>
+    <t>Matches McKinlay pick. Corresponds to a Gr/Resistivity and sonic shift to the right. First occurance of marker entered.</t>
+  </si>
+  <si>
+    <t>MCKINLAY 12</t>
+  </si>
+  <si>
+    <t>Matches McKinlay pick. Corresponds to a Gr/Resistivity and sonic shift to the right.</t>
+  </si>
+  <si>
+    <t>MCKINLAY 13</t>
+  </si>
+  <si>
+    <t>MCKINLAY 14</t>
+  </si>
+  <si>
+    <t>MCKINLAY 15</t>
   </si>
 </sst>
 </file>
@@ -519,7 +555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH19"/>
+  <dimension ref="A1:AH25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="41.28515625" customWidth="1"/>
@@ -1467,12 +1503,405 @@
         <v>37</v>
       </c>
     </row>
+    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>1263</v>
+      </c>
+      <c r="B20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20">
+        <v>25655223</v>
+      </c>
+      <c r="D20" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20">
+        <v>450054.94</v>
+      </c>
+      <c r="F20">
+        <v>6849914.6699999999</v>
+      </c>
+      <c r="G20">
+        <v>-1192.52</v>
+      </c>
+      <c r="H20">
+        <v>1579.69</v>
+      </c>
+      <c r="K20">
+        <v>-1192.52</v>
+      </c>
+      <c r="O20" t="s">
+        <v>35</v>
+      </c>
+      <c r="P20">
+        <v>1</v>
+      </c>
+      <c r="U20" t="b">
+        <v>1</v>
+      </c>
+      <c r="V20" t="b">
+        <v>1</v>
+      </c>
+      <c r="W20" t="s">
+        <v>36</v>
+      </c>
+      <c r="X20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC20">
+        <v>1</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>1385</v>
+      </c>
+      <c r="B21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21">
+        <v>25655225</v>
+      </c>
+      <c r="D21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21">
+        <v>449260.45</v>
+      </c>
+      <c r="F21">
+        <v>6849616.2699999996</v>
+      </c>
+      <c r="G21">
+        <v>-1195.94</v>
+      </c>
+      <c r="H21">
+        <v>1600.2</v>
+      </c>
+      <c r="K21">
+        <v>-1195.94</v>
+      </c>
+      <c r="O21" t="s">
+        <v>60</v>
+      </c>
+      <c r="P21">
+        <v>1</v>
+      </c>
+      <c r="U21" t="b">
+        <v>1</v>
+      </c>
+      <c r="V21" t="b">
+        <v>1</v>
+      </c>
+      <c r="W21" t="s">
+        <v>36</v>
+      </c>
+      <c r="X21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC21">
+        <v>1</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>1276</v>
+      </c>
+      <c r="B22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22">
+        <v>36386254</v>
+      </c>
+      <c r="D22" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22">
+        <v>450263.89</v>
+      </c>
+      <c r="F22">
+        <v>6851124.2199999997</v>
+      </c>
+      <c r="G22">
+        <v>-1196.6099999999999</v>
+      </c>
+      <c r="H22">
+        <v>1680.36</v>
+      </c>
+      <c r="K22">
+        <v>-1196.6099999999999</v>
+      </c>
+      <c r="O22" t="s">
+        <v>60</v>
+      </c>
+      <c r="P22">
+        <v>1</v>
+      </c>
+      <c r="U22" t="b">
+        <v>1</v>
+      </c>
+      <c r="V22" t="b">
+        <v>1</v>
+      </c>
+      <c r="W22" t="s">
+        <v>36</v>
+      </c>
+      <c r="X22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC22">
+        <v>1</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>1310</v>
+      </c>
+      <c r="B23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23">
+        <v>36393645</v>
+      </c>
+      <c r="D23" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23">
+        <v>449583.18</v>
+      </c>
+      <c r="F23">
+        <v>6849361.1500000004</v>
+      </c>
+      <c r="G23">
+        <v>-1194.93</v>
+      </c>
+      <c r="H23">
+        <v>1831.54</v>
+      </c>
+      <c r="K23">
+        <v>-1194.93</v>
+      </c>
+      <c r="O23" t="s">
+        <v>60</v>
+      </c>
+      <c r="P23">
+        <v>1</v>
+      </c>
+      <c r="U23" t="b">
+        <v>1</v>
+      </c>
+      <c r="V23" t="b">
+        <v>1</v>
+      </c>
+      <c r="W23" t="s">
+        <v>36</v>
+      </c>
+      <c r="X23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC23">
+        <v>1</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>1399</v>
+      </c>
+      <c r="B24" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24">
+        <v>36393646</v>
+      </c>
+      <c r="D24" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24">
+        <v>449059.36</v>
+      </c>
+      <c r="F24">
+        <v>6849093.8799999999</v>
+      </c>
+      <c r="G24">
+        <v>-1199.1099999999999</v>
+      </c>
+      <c r="H24">
+        <v>1832.76</v>
+      </c>
+      <c r="K24">
+        <v>-1199.1099999999999</v>
+      </c>
+      <c r="O24" t="s">
+        <v>60</v>
+      </c>
+      <c r="P24">
+        <v>1</v>
+      </c>
+      <c r="U24" t="b">
+        <v>1</v>
+      </c>
+      <c r="V24" t="b">
+        <v>1</v>
+      </c>
+      <c r="W24" t="s">
+        <v>36</v>
+      </c>
+      <c r="X24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC24">
+        <v>1</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>1270</v>
+      </c>
+      <c r="B25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25">
+        <v>36393647</v>
+      </c>
+      <c r="D25" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25">
+        <v>449479.85</v>
+      </c>
+      <c r="F25">
+        <v>6850444.2699999996</v>
+      </c>
+      <c r="G25">
+        <v>-1192.8399999999999</v>
+      </c>
+      <c r="H25">
+        <v>1717.85</v>
+      </c>
+      <c r="K25">
+        <v>-1192.8399999999999</v>
+      </c>
+      <c r="O25" t="s">
+        <v>60</v>
+      </c>
+      <c r="P25">
+        <v>1</v>
+      </c>
+      <c r="U25" t="b">
+        <v>1</v>
+      </c>
+      <c r="V25" t="b">
+        <v>1</v>
+      </c>
+      <c r="W25" t="s">
+        <v>36</v>
+      </c>
+      <c r="X25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC25">
+        <v>1</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c4de8975-a9e2-4032-8275-674640ba9e13" xsi:nil="true"/>
+    <Notes xmlns="525c6e3c-d2e9-4aaf-b2c8-6be610c2f5fd" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="525c6e3c-d2e9-4aaf-b2c8-6be610c2f5fd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F058933DE679D84C844BCD5E6FE280F8" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7c3559ca4b0718cc0d1b32599faf4d2a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="525c6e3c-d2e9-4aaf-b2c8-6be610c2f5fd" xmlns:ns3="416a3325-149f-4ed5-ad81-b499dd2029e2" xmlns:ns4="c4de8975-a9e2-4032-8275-674640ba9e13" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2290b9febe09ca40959ebaa4289d445c" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="525c6e3c-d2e9-4aaf-b2c8-6be610c2f5fd"/>
@@ -1740,28 +2169,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96E29180-4F03-4CC1-B8B1-E3BC1895BDE1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c4de8975-a9e2-4032-8275-674640ba9e13"/>
+    <ds:schemaRef ds:uri="525c6e3c-d2e9-4aaf-b2c8-6be610c2f5fd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c4de8975-a9e2-4032-8275-674640ba9e13" xsi:nil="true"/>
-    <Notes xmlns="525c6e3c-d2e9-4aaf-b2c8-6be610c2f5fd" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="525c6e3c-d2e9-4aaf-b2c8-6be610c2f5fd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D0B73D6-E817-4B19-AFB9-862FDFB2740C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CCAC797-B1FA-443B-8BE7-25249573A9A9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1781,25 +2208,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D0B73D6-E817-4B19-AFB9-862FDFB2740C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96E29180-4F03-4CC1-B8B1-E3BC1895BDE1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c4de8975-a9e2-4032-8275-674640ba9e13"/>
-    <ds:schemaRef ds:uri="525c6e3c-d2e9-4aaf-b2c8-6be610c2f5fd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{826c2670-3368-498f-a16b-70466cda23c0}" enabled="1" method="Standard" siteId="{447a9cb9-b230-46bf-b430-a7b9f50e3c1e}" removed="0"/>
